--- a/ert/input/distributions/design_input_one_by_one.xlsx
+++ b/ert/input/distributions/design_input_one_by_one.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="general_input" sheetId="1" state="visible" r:id="rId2"/>
@@ -730,7 +730,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="177">
   <si>
     <t xml:space="preserve">designtype</t>
   </si>
@@ -1176,18 +1176,6 @@
     <t xml:space="preserve">THERYS_APS_1_0_GF_GRF1_TREND_STACKANGLE</t>
   </si>
   <si>
-    <t xml:space="preserve">THERYS_APS_1_0_GF_GRF2_RESIDUAL_MAINRANGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THERYS_APS_1_0_GF_GRF2_RESIDUAL_PERPRANGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THERYS_APS_1_0_GF_GRF2_RESIDUAL_VERTRANGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THERYS_APS_1_0_GF_GRF2_RESIDUAL_AZIMUTHANGLE</t>
-  </si>
-  <si>
     <t xml:space="preserve">THERYS_APS_1_0_GF_GRF3_RESIDUAL_MAINRANGE</t>
   </si>
   <si>
@@ -1210,18 +1198,6 @@
   </si>
   <si>
     <t xml:space="preserve">VOLON_APS_1_0_GF_GRF1_RESIDUAL_AZIMUTHANGLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VOLON_APS_1_0_GF_GRF2_RESIDUAL_MAINRANGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VOLON_APS_1_0_GF_GRF2_RESIDUAL_PERPRANGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VOLON_APS_1_0_GF_GRF2_RESIDUAL_VERTRANGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VOLON_APS_1_0_GF_GRF2_RESIDUAL_AZIMUTHANGLE</t>
   </si>
   <si>
     <t xml:space="preserve">VOLON_APS_1_0_GF_GRF3_RESIDUAL_MAINRANGE</t>
@@ -1768,9 +1744,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>261720</xdr:colOff>
+      <xdr:colOff>260280</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>110880</xdr:rowOff>
+      <xdr:rowOff>109440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1780,7 +1756,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="8215560" cy="7601040"/>
+          <a:ext cx="8245800" cy="7599600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1813,9 +1789,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>261720</xdr:colOff>
+      <xdr:colOff>260280</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>110880</xdr:rowOff>
+      <xdr:rowOff>109440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1825,7 +1801,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="8215560" cy="7601040"/>
+          <a:ext cx="8245800" cy="7599600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1858,9 +1834,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>261720</xdr:colOff>
+      <xdr:colOff>260280</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>110880</xdr:rowOff>
+      <xdr:rowOff>109440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1870,7 +1846,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="8215560" cy="7601040"/>
+          <a:ext cx="8245800" cy="7599600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1908,9 +1884,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>165240</xdr:colOff>
+      <xdr:colOff>163800</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>34200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1920,7 +1896,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9069120" cy="4767480"/>
+          <a:ext cx="9067680" cy="4766040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1953,9 +1929,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>165240</xdr:colOff>
+      <xdr:colOff>163800</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>34200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1965,7 +1941,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9069120" cy="4767480"/>
+          <a:ext cx="9067680" cy="4766040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1998,9 +1974,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>165240</xdr:colOff>
+      <xdr:colOff>163800</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>34200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2010,7 +1986,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9069120" cy="4767480"/>
+          <a:ext cx="9067680" cy="4766040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2043,9 +2019,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>165240</xdr:colOff>
+      <xdr:colOff>163800</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>34200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2055,7 +2031,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9069120" cy="4767480"/>
+          <a:ext cx="9067680" cy="4766040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2088,9 +2064,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>165240</xdr:colOff>
+      <xdr:colOff>163800</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>34200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2100,7 +2076,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9069120" cy="4767480"/>
+          <a:ext cx="9067680" cy="4766040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2133,9 +2109,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>165240</xdr:colOff>
+      <xdr:colOff>163800</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>34200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2145,7 +2121,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9069120" cy="4767480"/>
+          <a:ext cx="9067680" cy="4766040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2178,9 +2154,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>165240</xdr:colOff>
+      <xdr:colOff>163800</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>34200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2190,7 +2166,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9069120" cy="4767480"/>
+          <a:ext cx="9067680" cy="4766040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2223,9 +2199,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>165240</xdr:colOff>
+      <xdr:colOff>163800</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>34200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2235,7 +2211,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9069120" cy="4767480"/>
+          <a:ext cx="9067680" cy="4766040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2268,9 +2244,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>165240</xdr:colOff>
+      <xdr:colOff>163800</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>34200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2280,7 +2256,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9069120" cy="4767480"/>
+          <a:ext cx="9067680" cy="4766040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2313,9 +2289,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>165240</xdr:colOff>
+      <xdr:colOff>163800</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>34200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2325,7 +2301,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9069120" cy="4767480"/>
+          <a:ext cx="9067680" cy="4766040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2358,9 +2334,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>165240</xdr:colOff>
+      <xdr:colOff>163800</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>34200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2370,7 +2346,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9069120" cy="4767480"/>
+          <a:ext cx="9067680" cy="4766040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2403,7 +2379,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.13"/>
@@ -2468,7 +2444,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q28"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="8.44"/>
@@ -3342,7 +3318,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B1048576"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="60.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.22"/>
@@ -4065,7 +4041,7 @@
         <v>141</v>
       </c>
       <c r="B90" s="40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4081,7 +4057,7 @@
         <v>143</v>
       </c>
       <c r="B92" s="39" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4089,7 +4065,7 @@
         <v>144</v>
       </c>
       <c r="B93" s="39" t="n">
-        <v>6000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4105,7 +4081,7 @@
         <v>146</v>
       </c>
       <c r="B95" s="39" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4121,7 +4097,7 @@
         <v>148</v>
       </c>
       <c r="B97" s="39" t="n">
-        <v>6000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4129,7 +4105,7 @@
         <v>149</v>
       </c>
       <c r="B98" s="39" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4137,7 +4113,7 @@
         <v>150</v>
       </c>
       <c r="B99" s="39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4153,7 +4129,7 @@
         <v>152</v>
       </c>
       <c r="B101" s="39" t="n">
-        <v>1500</v>
+        <v>900</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4161,7 +4137,7 @@
         <v>153</v>
       </c>
       <c r="B102" s="39" t="n">
-        <v>1500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4169,7 +4145,7 @@
         <v>154</v>
       </c>
       <c r="B103" s="39" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4177,7 +4153,7 @@
         <v>155</v>
       </c>
       <c r="B104" s="39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4185,7 +4161,7 @@
         <v>156</v>
       </c>
       <c r="B105" s="39" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4193,7 +4169,7 @@
         <v>157</v>
       </c>
       <c r="B106" s="39" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4201,7 +4177,7 @@
         <v>158</v>
       </c>
       <c r="B107" s="39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4209,113 +4185,57 @@
         <v>159</v>
       </c>
       <c r="B108" s="39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
         <v>160</v>
       </c>
-      <c r="B109" s="39" t="n">
-        <v>1000</v>
+      <c r="B109" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
         <v>161</v>
       </c>
-      <c r="B110" s="39" t="n">
-        <v>1000</v>
+      <c r="B110" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
         <v>162</v>
       </c>
-      <c r="B111" s="39" t="n">
-        <v>5</v>
+      <c r="B111" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B112" s="39" t="n">
-        <v>0</v>
+      <c r="B112" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="B113" s="39" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="0" t="s">
-        <v>165</v>
-      </c>
-      <c r="B114" s="39" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="0" t="s">
-        <v>166</v>
-      </c>
-      <c r="B115" s="39" t="n">
+      <c r="B113" s="1" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="0" t="s">
-        <v>167</v>
-      </c>
-      <c r="B116" s="39" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="0" t="s">
-        <v>168</v>
-      </c>
-      <c r="B117" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="0" t="s">
-        <v>169</v>
-      </c>
-      <c r="B118" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="B119" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="0" t="s">
-        <v>171</v>
-      </c>
-      <c r="B120" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="0" t="s">
-        <v>172</v>
-      </c>
-      <c r="B121" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
+    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -4345,58 +4265,58 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D9" s="41" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/ert/input/distributions/design_input_one_by_one.xlsx
+++ b/ert/input/distributions/design_input_one_by_one.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="general_input" sheetId="1" state="visible" r:id="rId2"/>
@@ -1768,9 +1768,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>261720</xdr:colOff>
+      <xdr:colOff>261360</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>110880</xdr:rowOff>
+      <xdr:rowOff>110520</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1780,7 +1780,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="8215560" cy="7601040"/>
+          <a:ext cx="8221680" cy="7600680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1813,9 +1813,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>261720</xdr:colOff>
+      <xdr:colOff>261360</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>110880</xdr:rowOff>
+      <xdr:rowOff>110520</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1825,7 +1825,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="8215560" cy="7601040"/>
+          <a:ext cx="8221680" cy="7600680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1858,9 +1858,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>261720</xdr:colOff>
+      <xdr:colOff>261360</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>110880</xdr:rowOff>
+      <xdr:rowOff>110520</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1870,7 +1870,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="8215560" cy="7601040"/>
+          <a:ext cx="8221680" cy="7600680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1908,9 +1908,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>165240</xdr:colOff>
+      <xdr:colOff>164880</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>35280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1920,7 +1920,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9069120" cy="4767480"/>
+          <a:ext cx="9068760" cy="4767120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1953,9 +1953,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>165240</xdr:colOff>
+      <xdr:colOff>164880</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>35280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1965,7 +1965,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9069120" cy="4767480"/>
+          <a:ext cx="9068760" cy="4767120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1998,9 +1998,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>165240</xdr:colOff>
+      <xdr:colOff>164880</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>35280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2010,7 +2010,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9069120" cy="4767480"/>
+          <a:ext cx="9068760" cy="4767120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2043,9 +2043,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>165240</xdr:colOff>
+      <xdr:colOff>164880</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>35280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2055,7 +2055,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9069120" cy="4767480"/>
+          <a:ext cx="9068760" cy="4767120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2088,9 +2088,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>165240</xdr:colOff>
+      <xdr:colOff>164880</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>35280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2100,7 +2100,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9069120" cy="4767480"/>
+          <a:ext cx="9068760" cy="4767120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2133,9 +2133,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>165240</xdr:colOff>
+      <xdr:colOff>164880</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>35280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2145,7 +2145,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9069120" cy="4767480"/>
+          <a:ext cx="9068760" cy="4767120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2178,9 +2178,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>165240</xdr:colOff>
+      <xdr:colOff>164880</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>35280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2190,7 +2190,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9069120" cy="4767480"/>
+          <a:ext cx="9068760" cy="4767120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2223,9 +2223,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>165240</xdr:colOff>
+      <xdr:colOff>164880</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>35280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2235,7 +2235,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9069120" cy="4767480"/>
+          <a:ext cx="9068760" cy="4767120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2268,9 +2268,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>165240</xdr:colOff>
+      <xdr:colOff>164880</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>35280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2280,7 +2280,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9069120" cy="4767480"/>
+          <a:ext cx="9068760" cy="4767120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2313,9 +2313,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>165240</xdr:colOff>
+      <xdr:colOff>164880</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>35280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2325,7 +2325,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9069120" cy="4767480"/>
+          <a:ext cx="9068760" cy="4767120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2358,9 +2358,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>165240</xdr:colOff>
+      <xdr:colOff>164880</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>35280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2370,7 +2370,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9069120" cy="4767480"/>
+          <a:ext cx="9068760" cy="4767120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2403,7 +2403,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.13"/>
@@ -2468,7 +2468,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q28"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="8.44"/>
@@ -3342,7 +3342,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B1048576"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="60.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.22"/>
@@ -4065,7 +4065,7 @@
         <v>141</v>
       </c>
       <c r="B90" s="40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4073,7 +4073,7 @@
         <v>142</v>
       </c>
       <c r="B91" s="40" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4081,7 +4081,7 @@
         <v>143</v>
       </c>
       <c r="B92" s="39" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4089,7 +4089,7 @@
         <v>144</v>
       </c>
       <c r="B93" s="39" t="n">
-        <v>6000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4105,7 +4105,7 @@
         <v>146</v>
       </c>
       <c r="B95" s="39" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4169,7 +4169,7 @@
         <v>154</v>
       </c>
       <c r="B103" s="39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4241,7 +4241,7 @@
         <v>163</v>
       </c>
       <c r="B112" s="39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4273,7 +4273,7 @@
         <v>167</v>
       </c>
       <c r="B116" s="39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4345,7 +4345,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
